--- a/astro-site/public/dl/pack-appcc/09-control-aceite-fritura.xlsx
+++ b/astro-site/public/dl/pack-appcc/09-control-aceite-fritura.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Control Aceite" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Aceite" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Control Aceite'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -115,27 +117,27 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -495,15 +497,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -511,6 +514,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -518,9 +522,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -556,13 +558,19 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" t="inlineStr"/>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -570,7 +578,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -579,19 +596,19 @@
   <sheetPr>
     <tabColor rgb="00FFC107"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="14"/>
-    <col customWidth="1" max="2" min="2" width="20"/>
-    <col customWidth="1" max="3" min="3" width="18"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="15"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="18"/>
-    <col customWidth="1" max="8" min="8" width="20"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -608,6 +625,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -910,6 +928,7 @@
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
@@ -929,11 +948,19 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24" type="list">
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Tiras reactivas,Medidor digital,Visual,Otro"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/pack-appcc/09-control-aceite-fritura.xlsx
+++ b/astro-site/public/dl/pack-appcc/09-control-aceite-fritura.xlsx
@@ -9,9 +9,14 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Aceite" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retirada de aceite usado" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Control Aceite'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Control Aceite'!$A$1:$H$50</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Retirada de aceite usado'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Retirada de aceite usado'!$A$1:$F$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,8 +24,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="9">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,8 +79,31 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -92,8 +122,18 @@
         <bgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D2D2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -115,11 +155,25 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -133,10 +187,85 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -499,16 +628,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Control de Aceite de Fritura</t>
         </is>
@@ -516,7 +645,7 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Cómo usar esta plantilla</t>
         </is>
@@ -524,61 +653,115 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>▸ Registra cada cambio de aceite y resultado de test</t>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>▸ Registra cada test de aceite en la hoja «Control Aceite»: fecha, freidora, método, % de compuestos polares y temperatura máxima alcanzada ese día.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>▸ El aceite debe cambiarse cuando supera el 25% de compuestos polares</t>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>▸ La columna «Estado» se calcula sola y se pinta: OK (verde), VIGILAR (ámbar) a partir del 20 % y CAMBIAR (rojo) al alcanzar el 25 % O al superar los 180 °C.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>▸ Temperatura máxima de fritura: 180°C</t>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>▸ Mide con tiras reactivas o con medidor digital de compuestos polares. El método «Visual» no es un control: úsalo sólo como apoyo.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>▸ Usa tiras reactivas o medidor digital de compuestos polares</t>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>▸ Anota cada retirada de aceite usado en la hoja «Retirada de aceite usado», con el gestor y el nº de documento.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>▸ Obligatorio según RD 2207/1995</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Límites que aplica la hoja</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>▸ Máximo 25 % de compuestos polares — Orden de 26 de enero de 1989 (Norma de Calidad para los aceites y grasas calentados). El 25,0 % clavado ya obliga a cambiar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>▸ Temperatura máxima de fritura recomendada: 180 °C. Por encima, el Estado dice CAMBIAR aunque el % de polares sea bajo o todavía no lo hayas medido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>▸ Si anotas sólo la temperatura y aún no has hecho el test, el Estado dice FALTA TEST en ámbar. La fila deja de estar en blanco: se ve que falta el dato, no que todo esté bien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>▸ El aceite usado es un residuo (LER 20 01 25): sólo lo retira un gestor autorizado y hay que guardar el justificante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Frecuencia y archivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>▸ Frecuencia recomendada: un test por freidora y semana en uso normal; diario si se fríe empanado o pescado a diario. La hoja trae 40 filas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>▸ Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
+    <row r="24"/>
+    <row r="25">
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2"/>
-  </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
@@ -598,21 +781,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Control de Aceite de Fritura</t>
         </is>
@@ -621,338 +804,991 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Freidora: ________________________    Tipo aceite: ________________________</t>
+          <t>Freidora: ________________________    Tipo de aceite: ________________________</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Freidora / Equipo</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Tipo de Test</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Resultado (%CP)</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Temp. Máx (°C)</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Freidora / equipo</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Tipo de test</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Resultado (% CP)</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Temp. máx. alcanzada (°C)</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Acción Realizada</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Acción realizada</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>Firma</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7">
-        <f>IF(D5="","",IF(D5&gt;25,"CAMBIAR",IF(D5&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="n"/>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7">
-        <f>IF(D6="","",IF(D6&gt;25,"CAMBIAR",IF(D6&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7">
-        <f>IF(D7="","",IF(D7&gt;25,"CAMBIAR",IF(D7&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7">
-        <f>IF(D8="","",IF(D8&gt;25,"CAMBIAR",IF(D8&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7">
-        <f>IF(D9="","",IF(D9&gt;25,"CAMBIAR",IF(D9&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7">
-        <f>IF(D10="","",IF(D10&gt;25,"CAMBIAR",IF(D10&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7">
-        <f>IF(D11="","",IF(D11&gt;25,"CAMBIAR",IF(D11&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7">
-        <f>IF(D12="","",IF(D12&gt;25,"CAMBIAR",IF(D12&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7">
-        <f>IF(D13="","",IF(D13&gt;25,"CAMBIAR",IF(D13&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7">
-        <f>IF(D14="","",IF(D14&gt;25,"CAMBIAR",IF(D14&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7">
-        <f>IF(D15="","",IF(D15&gt;25,"CAMBIAR",IF(D15&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7">
-        <f>IF(D16="","",IF(D16&gt;25,"CAMBIAR",IF(D16&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7">
-        <f>IF(D17="","",IF(D17&gt;25,"CAMBIAR",IF(D17&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7">
-        <f>IF(D18="","",IF(D18&gt;25,"CAMBIAR",IF(D18&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7">
-        <f>IF(D19="","",IF(D19&gt;25,"CAMBIAR",IF(D19&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7">
-        <f>IF(D20="","",IF(D20&gt;25,"CAMBIAR",IF(D20&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7">
-        <f>IF(D21="","",IF(D21&gt;25,"CAMBIAR",IF(D21&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7">
-        <f>IF(D22="","",IF(D22&gt;25,"CAMBIAR",IF(D22&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7">
-        <f>IF(D23="","",IF(D23&gt;25,"CAMBIAR",IF(D23&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7">
-        <f>IF(D24="","",IF(D24&gt;25,"CAMBIAR",IF(D24&gt;20,"VIGILAR","OK")))</f>
-        <v/>
-      </c>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>Límite legal: máx. 25% compuestos polares (RD 2207/1995). Cambiar aceite antes de superar este límite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Freidora 1</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Tiras reactivas</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>175</v>
+      </c>
+      <c r="F5" s="17" t="str">
+        <f>IF(AND($D5="",$E5=""),"",IF(IF($E5="",0,$E5)&gt;180,"CAMBIAR",IF($D5="","FALTA TEST",IF($D5&gt;=25,"CAMBIAR",IF($D5&gt;=20,"VIGILAR","OK")))))</f>
+        <v>OK</v>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>Filtrado y reposición de nivel (ejemplo)</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>A.R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Freidora 1</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Medidor digital</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>178</v>
+      </c>
+      <c r="F6" s="17" t="str">
+        <f>IF(AND($D6="",$E6=""),"",IF(IF($E6="",0,$E6)&gt;180,"CAMBIAR",IF($D6="","FALTA TEST",IF($D6&gt;=25,"CAMBIAR",IF($D6&gt;=20,"VIGILAR","OK")))))</f>
+        <v>VIGILAR</v>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>Vigilar: previsto cambio esta semana (ejemplo)</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>A.R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Freidora 2</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Medidor digital</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>180</v>
+      </c>
+      <c r="F7" s="17" t="str">
+        <f>IF(AND($D7="",$E7=""),"",IF(IF($E7="",0,$E7)&gt;180,"CAMBIAR",IF($D7="","FALTA TEST",IF($D7&gt;=25,"CAMBIAR",IF($D7&gt;=20,"VIGILAR","OK")))))</f>
+        <v>CAMBIAR</v>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>Cambio de aceite y limpieza de cuba (ejemplo)</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>M.S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="14" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="17">
+        <f>IF(AND($D8="",$E8=""),"",IF(IF($E8="",0,$E8)&gt;180,"CAMBIAR",IF($D8="","FALTA TEST",IF($D8&gt;=25,"CAMBIAR",IF($D8&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="14" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="14" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="17">
+        <f>IF(AND($D9="",$E9=""),"",IF(IF($E9="",0,$E9)&gt;180,"CAMBIAR",IF($D9="","FALTA TEST",IF($D9&gt;=25,"CAMBIAR",IF($D9&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="14" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="14" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="17">
+        <f>IF(AND($D10="",$E10=""),"",IF(IF($E10="",0,$E10)&gt;180,"CAMBIAR",IF($D10="","FALTA TEST",IF($D10&gt;=25,"CAMBIAR",IF($D10&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="14" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="17">
+        <f>IF(AND($D11="",$E11=""),"",IF(IF($E11="",0,$E11)&gt;180,"CAMBIAR",IF($D11="","FALTA TEST",IF($D11&gt;=25,"CAMBIAR",IF($D11&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="14" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="17">
+        <f>IF(AND($D12="",$E12=""),"",IF(IF($E12="",0,$E12)&gt;180,"CAMBIAR",IF($D12="","FALTA TEST",IF($D12&gt;=25,"CAMBIAR",IF($D12&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="14" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="14" t="n"/>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="17">
+        <f>IF(AND($D13="",$E13=""),"",IF(IF($E13="",0,$E13)&gt;180,"CAMBIAR",IF($D13="","FALTA TEST",IF($D13&gt;=25,"CAMBIAR",IF($D13&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="14" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="14" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="17">
+        <f>IF(AND($D14="",$E14=""),"",IF(IF($E14="",0,$E14)&gt;180,"CAMBIAR",IF($D14="","FALTA TEST",IF($D14&gt;=25,"CAMBIAR",IF($D14&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G14" s="15" t="n"/>
+      <c r="H14" s="14" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="14" t="n"/>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="17">
+        <f>IF(AND($D15="",$E15=""),"",IF(IF($E15="",0,$E15)&gt;180,"CAMBIAR",IF($D15="","FALTA TEST",IF($D15&gt;=25,"CAMBIAR",IF($D15&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G15" s="15" t="n"/>
+      <c r="H15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="14" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="17">
+        <f>IF(AND($D16="",$E16=""),"",IF(IF($E16="",0,$E16)&gt;180,"CAMBIAR",IF($D16="","FALTA TEST",IF($D16&gt;=25,"CAMBIAR",IF($D16&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G16" s="15" t="n"/>
+      <c r="H16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="14" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="17">
+        <f>IF(AND($D17="",$E17=""),"",IF(IF($E17="",0,$E17)&gt;180,"CAMBIAR",IF($D17="","FALTA TEST",IF($D17&gt;=25,"CAMBIAR",IF($D17&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="14" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="17">
+        <f>IF(AND($D18="",$E18=""),"",IF(IF($E18="",0,$E18)&gt;180,"CAMBIAR",IF($D18="","FALTA TEST",IF($D18&gt;=25,"CAMBIAR",IF($D18&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="14" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="17">
+        <f>IF(AND($D19="",$E19=""),"",IF(IF($E19="",0,$E19)&gt;180,"CAMBIAR",IF($D19="","FALTA TEST",IF($D19&gt;=25,"CAMBIAR",IF($D19&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="14" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="14" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="17">
+        <f>IF(AND($D20="",$E20=""),"",IF(IF($E20="",0,$E20)&gt;180,"CAMBIAR",IF($D20="","FALTA TEST",IF($D20&gt;=25,"CAMBIAR",IF($D20&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="14" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="14" t="n"/>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="17">
+        <f>IF(AND($D21="",$E21=""),"",IF(IF($E21="",0,$E21)&gt;180,"CAMBIAR",IF($D21="","FALTA TEST",IF($D21&gt;=25,"CAMBIAR",IF($D21&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="14" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="14" t="n"/>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="17">
+        <f>IF(AND($D22="",$E22=""),"",IF(IF($E22="",0,$E22)&gt;180,"CAMBIAR",IF($D22="","FALTA TEST",IF($D22&gt;=25,"CAMBIAR",IF($D22&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G22" s="15" t="n"/>
+      <c r="H22" s="14" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="14" t="n"/>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="17">
+        <f>IF(AND($D23="",$E23=""),"",IF(IF($E23="",0,$E23)&gt;180,"CAMBIAR",IF($D23="","FALTA TEST",IF($D23&gt;=25,"CAMBIAR",IF($D23&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G23" s="15" t="n"/>
+      <c r="H23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="14" t="n"/>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="17">
+        <f>IF(AND($D24="",$E24=""),"",IF(IF($E24="",0,$E24)&gt;180,"CAMBIAR",IF($D24="","FALTA TEST",IF($D24&gt;=25,"CAMBIAR",IF($D24&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G24" s="15" t="n"/>
+      <c r="H24" s="14" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="14" t="n"/>
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="17">
+        <f>IF(AND($D25="",$E25=""),"",IF(IF($E25="",0,$E25)&gt;180,"CAMBIAR",IF($D25="","FALTA TEST",IF($D25&gt;=25,"CAMBIAR",IF($D25&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G25" s="15" t="n"/>
+      <c r="H25" s="14" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="14" t="n"/>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="17">
+        <f>IF(AND($D26="",$E26=""),"",IF(IF($E26="",0,$E26)&gt;180,"CAMBIAR",IF($D26="","FALTA TEST",IF($D26&gt;=25,"CAMBIAR",IF($D26&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G26" s="15" t="n"/>
+      <c r="H26" s="14" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="14" t="n"/>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="17">
+        <f>IF(AND($D27="",$E27=""),"",IF(IF($E27="",0,$E27)&gt;180,"CAMBIAR",IF($D27="","FALTA TEST",IF($D27&gt;=25,"CAMBIAR",IF($D27&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G27" s="15" t="n"/>
+      <c r="H27" s="14" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="14" t="n"/>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="17">
+        <f>IF(AND($D28="",$E28=""),"",IF(IF($E28="",0,$E28)&gt;180,"CAMBIAR",IF($D28="","FALTA TEST",IF($D28&gt;=25,"CAMBIAR",IF($D28&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="14" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="14" t="n"/>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="17">
+        <f>IF(AND($D29="",$E29=""),"",IF(IF($E29="",0,$E29)&gt;180,"CAMBIAR",IF($D29="","FALTA TEST",IF($D29&gt;=25,"CAMBIAR",IF($D29&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="14" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="14" t="n"/>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="17">
+        <f>IF(AND($D30="",$E30=""),"",IF(IF($E30="",0,$E30)&gt;180,"CAMBIAR",IF($D30="","FALTA TEST",IF($D30&gt;=25,"CAMBIAR",IF($D30&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="14" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="14" t="n"/>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="17">
+        <f>IF(AND($D31="",$E31=""),"",IF(IF($E31="",0,$E31)&gt;180,"CAMBIAR",IF($D31="","FALTA TEST",IF($D31&gt;=25,"CAMBIAR",IF($D31&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G31" s="15" t="n"/>
+      <c r="H31" s="14" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="14" t="n"/>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="17">
+        <f>IF(AND($D32="",$E32=""),"",IF(IF($E32="",0,$E32)&gt;180,"CAMBIAR",IF($D32="","FALTA TEST",IF($D32&gt;=25,"CAMBIAR",IF($D32&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G32" s="15" t="n"/>
+      <c r="H32" s="14" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="14" t="n"/>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="16" t="n"/>
+      <c r="F33" s="17">
+        <f>IF(AND($D33="",$E33=""),"",IF(IF($E33="",0,$E33)&gt;180,"CAMBIAR",IF($D33="","FALTA TEST",IF($D33&gt;=25,"CAMBIAR",IF($D33&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G33" s="15" t="n"/>
+      <c r="H33" s="14" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="14" t="n"/>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="16" t="n"/>
+      <c r="F34" s="17">
+        <f>IF(AND($D34="",$E34=""),"",IF(IF($E34="",0,$E34)&gt;180,"CAMBIAR",IF($D34="","FALTA TEST",IF($D34&gt;=25,"CAMBIAR",IF($D34&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G34" s="15" t="n"/>
+      <c r="H34" s="14" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="14" t="n"/>
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="17">
+        <f>IF(AND($D35="",$E35=""),"",IF(IF($E35="",0,$E35)&gt;180,"CAMBIAR",IF($D35="","FALTA TEST",IF($D35&gt;=25,"CAMBIAR",IF($D35&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G35" s="15" t="n"/>
+      <c r="H35" s="14" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="14" t="n"/>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="17">
+        <f>IF(AND($D36="",$E36=""),"",IF(IF($E36="",0,$E36)&gt;180,"CAMBIAR",IF($D36="","FALTA TEST",IF($D36&gt;=25,"CAMBIAR",IF($D36&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G36" s="15" t="n"/>
+      <c r="H36" s="14" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="14" t="n"/>
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="17">
+        <f>IF(AND($D37="",$E37=""),"",IF(IF($E37="",0,$E37)&gt;180,"CAMBIAR",IF($D37="","FALTA TEST",IF($D37&gt;=25,"CAMBIAR",IF($D37&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G37" s="15" t="n"/>
+      <c r="H37" s="14" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="14" t="n"/>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="17">
+        <f>IF(AND($D38="",$E38=""),"",IF(IF($E38="",0,$E38)&gt;180,"CAMBIAR",IF($D38="","FALTA TEST",IF($D38&gt;=25,"CAMBIAR",IF($D38&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G38" s="15" t="n"/>
+      <c r="H38" s="14" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="14" t="n"/>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="16" t="n"/>
+      <c r="F39" s="17">
+        <f>IF(AND($D39="",$E39=""),"",IF(IF($E39="",0,$E39)&gt;180,"CAMBIAR",IF($D39="","FALTA TEST",IF($D39&gt;=25,"CAMBIAR",IF($D39&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G39" s="15" t="n"/>
+      <c r="H39" s="14" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="14" t="n"/>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="17">
+        <f>IF(AND($D40="",$E40=""),"",IF(IF($E40="",0,$E40)&gt;180,"CAMBIAR",IF($D40="","FALTA TEST",IF($D40&gt;=25,"CAMBIAR",IF($D40&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G40" s="15" t="n"/>
+      <c r="H40" s="14" t="n"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="14" t="n"/>
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="16" t="n"/>
+      <c r="E41" s="16" t="n"/>
+      <c r="F41" s="17">
+        <f>IF(AND($D41="",$E41=""),"",IF(IF($E41="",0,$E41)&gt;180,"CAMBIAR",IF($D41="","FALTA TEST",IF($D41&gt;=25,"CAMBIAR",IF($D41&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G41" s="15" t="n"/>
+      <c r="H41" s="14" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="14" t="n"/>
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="17">
+        <f>IF(AND($D42="",$E42=""),"",IF(IF($E42="",0,$E42)&gt;180,"CAMBIAR",IF($D42="","FALTA TEST",IF($D42&gt;=25,"CAMBIAR",IF($D42&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G42" s="15" t="n"/>
+      <c r="H42" s="14" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="14" t="n"/>
+      <c r="B43" s="15" t="n"/>
+      <c r="C43" s="15" t="n"/>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="16" t="n"/>
+      <c r="F43" s="17">
+        <f>IF(AND($D43="",$E43=""),"",IF(IF($E43="",0,$E43)&gt;180,"CAMBIAR",IF($D43="","FALTA TEST",IF($D43&gt;=25,"CAMBIAR",IF($D43&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G43" s="15" t="n"/>
+      <c r="H43" s="14" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="14" t="n"/>
+      <c r="B44" s="15" t="n"/>
+      <c r="C44" s="15" t="n"/>
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="17">
+        <f>IF(AND($D44="",$E44=""),"",IF(IF($E44="",0,$E44)&gt;180,"CAMBIAR",IF($D44="","FALTA TEST",IF($D44&gt;=25,"CAMBIAR",IF($D44&gt;=20,"VIGILAR","OK")))))</f>
+      </c>
+      <c r="G44" s="15" t="n"/>
+      <c r="H44" s="14" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46" ht="24.5" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>Límite legal: máx. 25 % de compuestos polares — Orden de 26 de enero de 1989, por la que se aprueba la Norma de Calidad para los aceites y grasas calentados. Cambiar el aceite al alcanzar el límite, no después: por eso 25,0 % ya dice CAMBIAR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="12.2" customHeight="1">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>Temperatura máxima de fritura recomendada: 180 °C. Por encima la degradación se dispara, así que el Estado también dice CAMBIAR aunque el % de polares sea bajo o no se haya medido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="12.2" customHeight="1">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>Si anotas la temperatura y todavía no has hecho el test de compuestos polares, el Estado dice FALTA TEST en ámbar: la fila no acredita nada hasta que lo completes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24.5" customHeight="1">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="12.2" customHeight="1">
+      <c r="A50" s="18" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
+    <row r="51"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="6">
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A48:H48"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A47:H47"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <conditionalFormatting sqref="F5:F44">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>OR(F5="ALERTA",F5="RECHAZAR",F5="CAMBIAR",F5="REVISAR",F5="✗",F5="CADUCADO",F5="EXCESO")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
+      <formula>OR(F5="VIGILAR",F5="⚠",F5="INCOMPLETO",F5="CADUCA PRONTO",F5="RENOVAR",F5="FALTA CLORO",F5="FALTA TEST",F5="FALTA TEST")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+      <formula>OR(F5="OK",F5="✓",F5="Cumple",F5="VIGENTE",F5="Completo",F5="APTO")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation sqref="C5:C44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Tipo de test" error="Elige un método de la lista." type="list" errorStyle="stop">
       <formula1>"Tiras reactivas,Medidor digital,Visual,Otro"</formula1>
     </dataValidation>
+    <dataValidation sqref="D5:D44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Compuestos polares" error="Introduce el % de compuestos polares, entre 0 y 50." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>50</formula2>
+    </dataValidation>
+    <dataValidation sqref="E5:E44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Temperatura máxima" error="Introduce la temperatura máxima alcanzada en °C, entre 0 y 250." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>250</formula2>
+    </dataValidation>
   </dataValidations>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Retirada de Aceite Usado por Gestor Autorizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>El aceite vegetal usado es un residuo no peligroso (LER 20 01 25): sólo puede retirarlo un gestor autorizado, y el justificante se pide en inspección junto al control de fritura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Litros retirados</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Gestor autorizado</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Nº autorización / documento</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Firma</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Recogidas Oleo S.L.</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>RET-2026-0915</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>M.S.</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>(ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="19" t="n"/>
+      <c r="B6" s="19" t="n"/>
+      <c r="C6" s="20" t="n"/>
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="20" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="19" t="n"/>
+      <c r="B7" s="19" t="n"/>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="19" t="n"/>
+      <c r="F7" s="20" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="19" t="n"/>
+      <c r="B8" s="19" t="n"/>
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="20" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="19" t="n"/>
+      <c r="B9" s="19" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="20" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="19" t="n"/>
+      <c r="B10" s="19" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="20" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="19" t="n"/>
+      <c r="B11" s="19" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="20" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="19" t="n"/>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="20" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="19" t="n"/>
+      <c r="B13" s="19" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="20" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="19" t="n"/>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="20" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="19" t="n"/>
+      <c r="B15" s="19" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="20" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="19" t="n"/>
+      <c r="B16" s="19" t="n"/>
+      <c r="C16" s="20" t="n"/>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="20" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="19" t="n"/>
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="20" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="19" t="n"/>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="20" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="19" t="n"/>
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="20" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="19" t="n"/>
+      <c r="B20" s="19" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="20" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="19" t="n"/>
+      <c r="B21" s="19" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="20" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="19" t="n"/>
+      <c r="B22" s="19" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="20" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="19" t="n"/>
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="20" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="20" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="19" t="n"/>
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="20" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="20" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="n"/>
+      <c r="B25" s="19" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="20" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="19" t="n"/>
+      <c r="B26" s="19" t="n"/>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="19" t="n"/>
+      <c r="F26" s="20" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="19" t="n"/>
+      <c r="B27" s="19" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="20" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="19" t="n"/>
+      <c r="B28" s="19" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="19" t="n"/>
+      <c r="F28" s="20" t="n"/>
+    </row>
+    <row r="29"/>
+    <row r="30" ht="24.5" customHeight="1">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>Guarda el justificante de cada retirada junto con este registro. Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="12.2" customHeight="1">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A30:F30"/>
+  </mergeCells>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>

--- a/astro-site/public/dl/pack-appcc/09-control-aceite-fritura.xlsx
+++ b/astro-site/public/dl/pack-appcc/09-control-aceite-fritura.xlsx
@@ -1445,12 +1445,12 @@
     <row r="51"/>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A49:H49"/>
     <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F44">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
@@ -1785,8 +1785,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A30:F30"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
